--- a/reports/二级子公司C_现金流量表_2025-09.xlsx
+++ b/reports/二级子公司C_现金流量表_2025-09.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>81900000</v>
+        <v>81496409</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>710580000</v>
+        <v>710156930</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1646092</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>14223748</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>815367</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>7098518</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>410920</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3556766</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>326900</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2839371</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>245843</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2133611</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>163969</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1420269</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>122538</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1066199</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>82210</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>710608</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>203803</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1775769</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>103413</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>893394</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>64786</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>564301</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>210000</v>
+        <v>210875</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1822000</v>
+        <v>1823929</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1575000</v>
+        <v>1570169</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>13665000</v>
+        <v>13650188</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>83685000</v>
+        <v>87463294</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>52500000</v>
+        <v>52284433</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>455500000</v>
+        <v>455429954</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>548622</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>4739520</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>407454</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3550150</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>274274</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2370914</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>203962</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1774533</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>136859</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1185565</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>102783</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>891936</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>8925000</v>
+        <v>8920750</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>77435000</v>
+        <v>77490959</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>4410000</v>
+        <v>4418994</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>38262000</v>
+        <v>38245727</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1890000</v>
+        <v>1883594</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>16398000</v>
+        <v>16399369</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>67725000</v>
+        <v>69181725</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>15960000</v>
+        <v>18281569</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>100000</v>
+        <v>100061</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>900000</v>
+        <v>900803</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>800000</v>
+        <v>797991</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>7200000</v>
+        <v>7202127</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>500000</v>
+        <v>501880</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>4500000</v>
+        <v>4500305</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>900000</v>
+        <v>898052</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6000000</v>
+        <v>6029926</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>54000000</v>
+        <v>54039700</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>800000</v>
+        <v>796129</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>7200000</v>
+        <v>7193017</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4500000</v>
+        <v>4518827</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>40500000</v>
+        <v>40544682</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>200000</v>
+        <v>199697</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1800000</v>
+        <v>1800942</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6200000</v>
+        <v>6229623</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5300000</v>
+        <v>-5331571</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>2000000</v>
+        <v>1990007</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>18000000</v>
+        <v>17985209</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>3000000</v>
+        <v>2988390</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>27000000</v>
+        <v>26969701</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>3000000</v>
+        <v>3007973</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>27000000</v>
+        <v>27029738</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>100000</v>
+        <v>99883</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>900000</v>
+        <v>899131</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>5100000</v>
+        <v>5078280</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2500000</v>
+        <v>2505028</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>22500000</v>
+        <v>22490649</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2500000</v>
+        <v>2491583</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>22500000</v>
+        <v>22501332</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>400000</v>
+        <v>401748</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3600000</v>
+        <v>3601093</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>350000</v>
+        <v>351732</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3150000</v>
+        <v>3152832</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>50000</v>
+        <v>49777</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>450000</v>
+        <v>449519</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2950000</v>
+        <v>2956553</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>2150000</v>
+        <v>2121727</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>12810000</v>
+        <v>15071725</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>12810000</v>
+        <v>15071725</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
